--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,26 +452,100 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Immunization.extension:basedOn</t>
-  </si>
-  <si>
-    <t>basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-ext-immunization-basedOn}
+    <t>Immunization.extension:ImmunizationBasedOnR5</t>
+  </si>
+  <si>
+    <t>ImmunizationBasedOnR5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Immunization.basedOn}
 </t>
   </si>
   <si>
-    <t>Immunization basedOn</t>
-  </si>
-  <si>
     <t>Authority that the immunization event is based on</t>
+  </si>
+  <si>
+    <t>This extension implements the R5 basedOn element. A plan, order or recommendation fulfilled in whole or in part by this immunization.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Immunization.extension:ImmunizationBasedOnR5.id</t>
+  </si>
+  <si>
+    <t>Immunization.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationBasedOnR5.extension</t>
+  </si>
+  <si>
+    <t>Immunization.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationBasedOnR5.url</t>
+  </si>
+  <si>
+    <t>Immunization.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-Immunization.basedOn</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationBasedOnR5.value[x]</t>
+  </si>
+  <si>
+    <t>Immunization.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|ServiceRequest|ImmunizationRecommendation)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
     <t>Immunization.modifierExtension</t>
   </si>
   <si>
@@ -785,7 +859,7 @@
     <t>Immunization.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -805,10 +879,6 @@
   </si>
   <si>
     <t>Immunization.lotNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Vaccine lot number</t>
@@ -934,18 +1004,6 @@
     <t>Immunization.performer.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Immunization.performer.extension</t>
   </si>
   <si>
@@ -953,9 +1011,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Immunization.performer.modifierExtension</t>
@@ -999,7 +1054,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1067,7 +1122,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport)
 </t>
   </si>
   <si>
@@ -1252,7 +1307,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -1663,12 +1718,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.25" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.4609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.25" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.80078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1676,7 +1731,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="76.62890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="174.80859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1694,7 +1749,7 @@
     <col min="26" max="26" width="59.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2779,7 +2834,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>79</v>
@@ -2869,7 +2924,7 @@
         <v>79</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>79</v>
@@ -2883,43 +2938,39 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -2967,28 +3018,28 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>79</v>
@@ -3002,7 +3053,7 @@
         <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3013,7 +3064,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>79</v>
@@ -3025,13 +3076,13 @@
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3070,19 +3121,19 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3094,30 +3145,30 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3134,22 +3185,22 @@
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3157,7 +3208,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -3175,13 +3226,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3199,7 +3250,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3211,19 +3262,19 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3231,10 +3282,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3242,7 +3293,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -3257,17 +3308,15 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3292,13 +3341,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3316,7 +3365,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3331,13 +3380,13 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>79</v>
@@ -3348,42 +3397,46 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -3407,11 +3460,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3429,42 +3484,42 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3472,10 +3527,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
@@ -3484,16 +3539,16 @@
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3544,13 +3599,13 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
@@ -3559,27 +3614,27 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3587,7 +3642,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3596,21 +3651,23 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3635,13 +3692,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3659,10 +3716,10 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>89</v>
@@ -3674,16 +3731,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3691,10 +3748,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3702,7 +3759,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3714,19 +3771,19 @@
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3752,13 +3809,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3776,10 +3833,10 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -3791,27 +3848,27 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3819,7 +3876,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3831,16 +3888,16 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3867,13 +3924,11 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3891,10 +3946,10 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3906,27 +3961,27 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3934,7 +3989,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3949,17 +4004,15 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4008,10 +4061,10 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -4023,16 +4076,16 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4040,10 +4093,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4066,17 +4119,15 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4101,13 +4152,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4125,7 +4176,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4140,13 +4191,13 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>229</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>231</v>
@@ -4157,10 +4208,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4168,7 +4219,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -4180,18 +4231,20 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4240,10 +4293,10 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>89</v>
@@ -4255,27 +4308,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4298,13 +4351,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4355,7 +4408,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4373,24 +4426,24 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4410,18 +4463,20 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4470,7 +4525,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4488,24 +4543,24 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>260</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4528,15 +4583,17 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4561,13 +4618,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4585,7 +4642,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4603,13 +4660,13 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4617,10 +4674,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4643,13 +4700,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4676,13 +4733,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4700,7 +4757,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4715,27 +4772,27 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4758,13 +4815,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4791,11 +4848,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4813,7 +4872,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4831,24 +4890,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4871,13 +4930,13 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4928,7 +4987,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4946,24 +5005,24 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4974,7 +5033,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -4983,16 +5042,16 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5043,13 +5102,13 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
@@ -5058,13 +5117,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5075,10 +5134,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5101,13 +5160,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5134,13 +5193,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5158,7 +5217,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5170,41 +5229,41 @@
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5216,17 +5275,15 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5251,13 +5308,11 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5275,78 +5330,74 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5394,28 +5445,28 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>132</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>79</v>
@@ -5426,10 +5477,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5440,7 +5491,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5452,13 +5503,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5485,13 +5536,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5509,13 +5560,13 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
@@ -5524,13 +5575,13 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
@@ -5541,10 +5592,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5552,7 +5603,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -5564,20 +5615,18 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>317</v>
+        <v>149</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5626,10 +5675,10 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>152</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>89</v>
@@ -5638,19 +5687,19 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>322</v>
+        <v>153</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5658,14 +5707,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5681,18 +5730,20 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>325</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5741,7 +5792,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5753,16 +5804,16 @@
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>330</v>
+        <v>153</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5773,14 +5824,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5793,22 +5844,26 @@
         <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -5832,13 +5887,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5856,7 +5911,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5868,16 +5923,16 @@
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>337</v>
+        <v>132</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -5888,10 +5943,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5902,7 +5957,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -5911,16 +5966,16 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>339</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5947,13 +6002,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5971,13 +6026,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -5986,13 +6041,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>132</v>
+        <v>333</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6003,10 +6058,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6014,7 +6069,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -6023,30 +6078,28 @@
         <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>225</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q38" t="s" s="2">
-        <v>346</v>
-      </c>
+      <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6090,10 +6143,10 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>89</v>
@@ -6105,16 +6158,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>132</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6122,10 +6175,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6145,16 +6198,16 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>173</v>
+        <v>343</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6181,13 +6234,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6205,7 +6258,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6220,13 +6273,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>132</v>
+        <v>348</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6237,10 +6290,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6263,13 +6316,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6296,13 +6349,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6320,7 +6373,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6332,16 +6385,16 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>356</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>132</v>
+        <v>355</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6352,10 +6405,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6366,7 +6419,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6378,13 +6431,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>255</v>
+        <v>357</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>297</v>
+        <v>358</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6435,28 +6488,28 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>299</v>
+        <v>132</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6467,48 +6520,50 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>249</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>151</v>
+        <v>363</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q42" s="2"/>
+      <c r="Q42" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="R42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6552,28 +6607,28 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>299</v>
+        <v>132</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6584,14 +6639,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6604,26 +6659,22 @@
         <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6647,13 +6698,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6671,7 +6722,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6683,7 +6734,7 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -6703,10 +6754,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6717,7 +6768,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6729,13 +6780,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6786,25 +6837,25 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>374</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>132</v>
@@ -6818,10 +6869,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6844,13 +6895,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>365</v>
+        <v>150</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>366</v>
+        <v>151</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6901,7 +6952,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>152</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6913,7 +6964,7 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -6922,7 +6973,7 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -6933,21 +6984,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -6959,15 +7010,17 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7016,28 +7069,28 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
@@ -7048,42 +7101,46 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7131,25 +7188,25 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>132</v>
@@ -7163,10 +7220,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7177,7 +7234,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -7189,13 +7246,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7222,37 +7279,37 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
@@ -7264,7 +7321,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>132</v>
@@ -7278,10 +7335,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7304,13 +7361,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7337,13 +7394,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7361,7 +7418,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7393,10 +7450,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7407,7 +7464,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7419,17 +7476,15 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>389</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7478,13 +7533,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -7496,10 +7551,10 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>391</v>
+        <v>132</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -7510,10 +7565,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7536,13 +7591,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>297</v>
+        <v>391</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7593,7 +7648,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>298</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7605,16 +7660,16 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>299</v>
+        <v>132</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -7632,7 +7687,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7651,17 +7706,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7686,13 +7739,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7710,7 +7763,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>303</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7722,16 +7775,16 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>299</v>
+        <v>132</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -7742,46 +7795,42 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -7805,13 +7854,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7829,19 +7878,19 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -7861,10 +7910,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7875,7 +7924,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -7887,15 +7936,17 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>312</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -7944,13 +7995,13 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
@@ -7962,10 +8013,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>215</v>
+        <v>409</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -7976,10 +8027,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8002,13 +8053,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>400</v>
+        <v>149</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>150</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>151</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8059,7 +8110,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>152</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8071,16 +8122,16 @@
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>153</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8091,21 +8142,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8117,15 +8168,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>320</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8174,28 +8227,28 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>157</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>409</v>
+        <v>153</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8206,18 +8259,18 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>81</v>
@@ -8226,22 +8279,26 @@
         <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>289</v>
+        <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8289,7 +8346,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>410</v>
+        <v>326</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8301,7 +8358,7 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8347,13 +8404,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>296</v>
+        <v>414</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>297</v>
+        <v>415</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8404,7 +8461,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8416,16 +8473,16 @@
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8436,21 +8493,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8462,17 +8519,15 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>134</v>
+        <v>418</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>301</v>
+        <v>419</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -8521,28 +8576,28 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>303</v>
+        <v>417</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>299</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -8553,46 +8608,42 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>249</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>306</v>
+        <v>424</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -8640,28 +8691,28 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>308</v>
+        <v>423</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>132</v>
+        <v>427</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -8672,10 +8723,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8683,10 +8734,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -8698,13 +8749,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8755,13 +8806,13 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
@@ -8787,10 +8838,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8813,13 +8864,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>248</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>421</v>
+        <v>151</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8870,7 +8921,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8882,7 +8933,7 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -8891,7 +8942,7 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -8902,18 +8953,18 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
@@ -8928,15 +8979,17 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>423</v>
+        <v>320</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -8961,11 +9014,13 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -8983,7 +9038,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>422</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8995,7 +9050,7 @@
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
@@ -9004,7 +9059,7 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9015,44 +9070,46 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>324</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>429</v>
+        <v>325</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9100,19 +9157,19 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>426</v>
+        <v>326</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
@@ -9132,10 +9189,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9158,17 +9215,15 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>427</v>
+        <v>149</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9217,7 +9272,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9244,6 +9299,468 @@
         <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y67" s="2"/>
+      <c r="Z67" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>79</v>
       </c>
     </row>
